--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:R9"/>
+  <dimension ref="B2:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-09 02:50 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-09 12:42 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Nike Zoom Kobe 5 Protro Dodgers 舒适贴合 支撑 低帮 篮球鞋 男款 蓝色</t>
+          <t>CAMEL骆驼 户外轻薄600蓬90%绒防风保暖抗静电轻量防钻绒不臃肿排骨羽绒服 男女同款</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>1399</v>
+        <v>201</v>
       </c>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6">
@@ -633,10 +633,10 @@
         <v/>
       </c>
       <c r="O5" s="5" t="n">
-        <v>1910.1</v>
+        <v>397.89</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>247.79</v>
+        <v>138.12</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -645,19 +645,19 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12213547</t>
+          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12214237</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>始祖鸟 GRANVILLE 10L 斜挎包</t>
+          <t>Nike Zoom Kobe 5 Protro Dodgers 舒适贴合 支撑 低帮 篮球鞋 男款 蓝色</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="9" t="n">
-        <v>1349</v>
+        <v>1399</v>
       </c>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10">
@@ -686,31 +686,31 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1851.5</v>
+        <v>1910.1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>283.84</v>
+        <v>247.79</v>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>可蹲</t>
+          <t>冷门优选</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=11610567</t>
+          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12213547</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PUMA Caven 2.0 小白鞋</t>
+          <t>始祖鸟 GRANVILLE 10L 斜挎包</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="5" t="n">
-        <v>170</v>
+        <v>1349</v>
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="6">
@@ -739,24 +739,77 @@
         <v/>
       </c>
       <c r="O7" s="5" t="n">
+        <v>1851.5</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>283.84</v>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>可蹲</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=11610567</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>PUMA Caven 2.0 小白鞋</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10">
+        <f>IFERROR(IF(OR(D8="",E8=""),"",(E8-D8)/D8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(OR(D8="",I8=""),"",I8*(1-J8)-D8-K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="8">
+        <f>IF(H8="","",IF(H8&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="N8" s="8">
+        <f>IF(OR(D8="",E8=""),"",IF(F8&lt;0.15,"放弃",IF(AND(H8&gt;=3,L8&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="O8" s="9" t="n">
         <v>274.2</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="P8" s="9" t="n">
         <v>53.55</v>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>可蹲</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>https://deal.mendaoapp.com/page/carry-referee?carryId=11611203</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>用法：得物App核价填E列 -&gt; 买1-2件 -&gt; 卖出后补G/H/I列；「加仓」条件=价差率≥15%且满3单且单均净利≥25元，公式自动判定。D列货源价来自门道到手价，下单前自行复核。</t>
         </is>
@@ -765,7 +818,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B9:R9"/>
+    <mergeCell ref="B10:R10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -505,7 +505,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-09 12:42 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-09 18:41 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -88,10 +88,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -100,10 +100,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -479,118 +479,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:R10"/>
+  <dimension ref="B2:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-09 18:41 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 00:04 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>候选品</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>试销日期</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>购入日期</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>货源价(元)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>得物核价(元)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>核价后价差率</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>试销件数</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>已卖出件数</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>卖出均价(元)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>平台费率</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>快递费(元/件)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>单均净利(元)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>满3单？</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>加仓决策</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>得物价参考</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>参考净利(元)</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>门道链接</t>
         </is>
@@ -599,51 +611,57 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>12214237</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
           <t>CAMEL骆驼 户外轻薄600蓬90%绒防风保暖抗静电轻量防钻绒不臃肿排骨羽绒服 男女同款</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="5" t="n">
         <v>201</v>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="6">
-        <f>IFERROR(IF(OR(D5="",E5=""),"",(E5-D5)/D5),"")</f>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="6">
+        <f>IFERROR(IF(OR(F5="",G5=""),"",(G5-F5)/F5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="5">
-        <f>IF(OR(D5="",I5=""),"",I5*(1-J5)-D5-K5)</f>
+      <c r="N5" s="5">
+        <f>IF(OR(F5="",K5=""),"",K5*(1-L5)-F5-M5)</f>
         <v/>
       </c>
-      <c r="M5" s="4">
-        <f>IF(H5="","",IF(H5&gt;=3,"是","否"))</f>
+      <c r="O5" s="3">
+        <f>IF(J5="","",IF(J5&gt;=3,"是","否"))</f>
         <v/>
       </c>
-      <c r="N5" s="4">
-        <f>IF(OR(D5="",E5=""),"",IF(F5&lt;0.15,"放弃",IF(AND(H5&gt;=3,L5&gt;=25),"加仓","观察")))</f>
+      <c r="P5" s="3">
+        <f>IF(OR(F5="",G5=""),"",IF(H5&lt;0.15,"放弃",IF(AND(J5&gt;=3,N5&gt;=25),"加仓","观察")))</f>
         <v/>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>397.89</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="R5" s="5" t="n">
         <v>138.12</v>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>冷门优选</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12214237</t>
         </is>
@@ -652,173 +670,73 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="7" t="inlineStr">
         <is>
+          <t>12213547</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
           <t>Nike Zoom Kobe 5 Protro Dodgers 舒适贴合 支撑 低帮 篮球鞋 男款 蓝色</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="9" t="n">
         <v>1399</v>
       </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="10">
-        <f>IFERROR(IF(OR(D6="",E6=""),"",(E6-D6)/D6),"")</f>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10">
+        <f>IFERROR(IF(OR(F6="",G6=""),"",(G6-F6)/F6),"")</f>
         <v/>
       </c>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="10" t="n">
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="M6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="9">
-        <f>IF(OR(D6="",I6=""),"",I6*(1-J6)-D6-K6)</f>
+      <c r="N6" s="9">
+        <f>IF(OR(F6="",K6=""),"",K6*(1-L6)-F6-M6)</f>
         <v/>
       </c>
-      <c r="M6" s="8">
-        <f>IF(H6="","",IF(H6&gt;=3,"是","否"))</f>
+      <c r="O6" s="7">
+        <f>IF(J6="","",IF(J6&gt;=3,"是","否"))</f>
         <v/>
       </c>
-      <c r="N6" s="8">
-        <f>IF(OR(D6="",E6=""),"",IF(F6&lt;0.15,"放弃",IF(AND(H6&gt;=3,L6&gt;=25),"加仓","观察")))</f>
+      <c r="P6" s="7">
+        <f>IF(OR(F6="",G6=""),"",IF(H6&lt;0.15,"放弃",IF(AND(J6&gt;=3,N6&gt;=25),"加仓","观察")))</f>
         <v/>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="Q6" s="9" t="n">
         <v>1910.1</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="R6" s="9" t="n">
         <v>247.79</v>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
         <is>
           <t>冷门优选</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12213547</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>始祖鸟 GRANVILLE 10L 斜挎包</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="n">
-        <v>1349</v>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="6">
-        <f>IFERROR(IF(OR(D7="",E7=""),"",(E7-D7)/D7),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="5">
-        <f>IF(OR(D7="",I7=""),"",I7*(1-J7)-D7-K7)</f>
-        <v/>
-      </c>
-      <c r="M7" s="4">
-        <f>IF(H7="","",IF(H7&gt;=3,"是","否"))</f>
-        <v/>
-      </c>
-      <c r="N7" s="4">
-        <f>IF(OR(D7="",E7=""),"",IF(F7&lt;0.15,"放弃",IF(AND(H7&gt;=3,L7&gt;=25),"加仓","观察")))</f>
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1851.5</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>283.84</v>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>可蹲</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=11610567</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>PUMA Caven 2.0 小白鞋</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="10">
-        <f>IFERROR(IF(OR(D8="",E8=""),"",(E8-D8)/D8),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="9">
-        <f>IF(OR(D8="",I8=""),"",I8*(1-J8)-D8-K8)</f>
-        <v/>
-      </c>
-      <c r="M8" s="8">
-        <f>IF(H8="","",IF(H8&gt;=3,"是","否"))</f>
-        <v/>
-      </c>
-      <c r="N8" s="8">
-        <f>IF(OR(D8="",E8=""),"",IF(F8&lt;0.15,"放弃",IF(AND(H8&gt;=3,L8&gt;=25),"加仓","观察")))</f>
-        <v/>
-      </c>
-      <c r="O8" s="9" t="n">
-        <v>274.2</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>可蹲</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=11611203</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>用法：得物App核价填E列 -&gt; 买1-2件 -&gt; 卖出后补G/H/I列；「加仓」条件=价差率≥15%且满3单且单均净利≥25元，公式自动判定。D列货源价来自门道到手价，下单前自行复核。</t>
+    <row r="8" ht="42" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>用法：①B列ID勿删（核价结果回传就靠它）②得物App核价填G列、购买当天E列记购入日期（月底誊到账单）③卖出后补I/J/K列；「加仓」=价差率≥15%且满3单且单均净利≥25元，公式自动判定。F列券后价来自联盟API，下单前自行复核。核完价把文件交回给助手回传，站点即自动算净利排序。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B10:R10"/>
+    <mergeCell ref="B8:T8"/>
+    <mergeCell ref="B2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 00:04 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 04:32 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -46,7 +46,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FB"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -81,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -97,18 +92,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -479,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T8"/>
+  <dimension ref="B2:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -507,7 +490,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 04:32 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 12:08 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -611,18 +594,18 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>12214237</t>
+          <t>12213547</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CAMEL骆驼 户外轻薄600蓬90%绒防风保暖抗静电轻量防钻绒不臃肿排骨羽绒服 男女同款</t>
+          <t>Nike Zoom Kobe 5 Protro Dodgers 舒适贴合 支撑 低帮 篮球鞋 男款 蓝色</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="5" t="n">
-        <v>201</v>
+        <v>1399</v>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="6">
@@ -651,83 +634,24 @@
         <v/>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>397.89</v>
+        <v>1897.75</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>138.12</v>
+        <v>237.04</v>
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>冷门优选</t>
+          <t>冷门优选·¥1910.1→¥1897.75 (-0.6%)</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12214237</t>
+          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12213547</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>12213547</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Nike Zoom Kobe 5 Protro Dodgers 舒适贴合 支撑 低帮 篮球鞋 男款 蓝色</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1399</v>
-      </c>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="10">
-        <f>IFERROR(IF(OR(F6="",G6=""),"",(G6-F6)/F6),"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" s="9">
-        <f>IF(OR(F6="",K6=""),"",K6*(1-L6)-F6-M6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="7">
-        <f>IF(J6="","",IF(J6&gt;=3,"是","否"))</f>
-        <v/>
-      </c>
-      <c r="P6" s="7">
-        <f>IF(OR(F6="",G6=""),"",IF(H6&lt;0.15,"放弃",IF(AND(J6&gt;=3,N6&gt;=25),"加仓","观察")))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="9" t="n">
-        <v>1910.1</v>
-      </c>
-      <c r="R6" s="9" t="n">
-        <v>247.79</v>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>冷门优选</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12213547</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>用法：①B列ID勿删（核价结果回传就靠它）②得物App核价填G列、购买当天E列记购入日期（月底誊到账单）③卖出后补I/J/K列；「加仓」=价差率≥15%且满3单且单均净利≥25元，公式自动判定。F列券后价来自联盟API，下单前自行复核。核完价把文件交回给助手回传，站点即自动算净利排序。</t>
         </is>
@@ -735,8 +659,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B8:T8"/>
     <mergeCell ref="B2:T2"/>
+    <mergeCell ref="B7:T7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -46,7 +46,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -92,6 +97,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -462,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T7"/>
+  <dimension ref="B2:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -490,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 12:08 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 16:25 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -594,18 +611,18 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>12213547</t>
+          <t>jd-MHQuhJJgthDWOX9y5MOtWOX9y5MOtQ_3RTWn2HSdluOqXJg5U</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Nike Zoom Kobe 5 Protro Dodgers 舒适贴合 支撑 低帮 篮球鞋 男款 蓝色</t>
+          <t>石头（roborock）【保价双11】扫地机器人扫拖一体 P30 Pro 自动上下水版 滚筒洗地机器人热水洗擦地拖地 A3060RR</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="5" t="n">
-        <v>1399</v>
+        <v>3797.32</v>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="6">
@@ -633,25 +650,791 @@
         <f>IF(OR(F5="",G5=""),"",IF(H5&lt;0.15,"放弃",IF(AND(J5&gt;=3,N5&gt;=25),"加仓","观察")))</f>
         <v/>
       </c>
-      <c r="Q5" s="5" t="n">
-        <v>1897.75</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>237.04</v>
-      </c>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>冷门优选·¥1910.1→¥1897.75 (-0.6%)</t>
+          <t>待核价</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>https://deal.mendaoapp.com/page/carry-referee?carryId=12213547</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="B7" s="7" t="inlineStr">
+          <t>https://item.jd.com/MHQuhJJgthDWOX9y5MOtWOX9y5MOtQ_3RTWn2HSdluOqXJg5U.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>jd-Ee4W5PRJj07hoEn0kh2uhoEn0kh2u4_3tyFw3LoavWozsxaal</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>科沃斯T90S PRO扫地机器人【保价11.11】扫拖一体自动清洗自动集尘热水洗拖布滚筒洗地机器人上下水款</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="9" t="n">
+        <v>3698.09</v>
+      </c>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10">
+        <f>IFERROR(IF(OR(F6="",G6=""),"",(G6-F6)/F6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(OR(F6="",K6=""),"",K6*(1-L6)-F6-M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="7">
+        <f>IF(J6="","",IF(J6&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P6" s="7">
+        <f>IF(OR(F6="",G6=""),"",IF(H6&lt;0.15,"放弃",IF(AND(J6&gt;=3,N6&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/Ee4W5PRJj07hoEn0kh2uhoEn0kh2u4_3tyFw3LoavWozsxaal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>jd-4MQRwdxjRz5YjYNYidARYjYNYidARQ_3uiI4idr4VRjmIMQeI</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>石头（roborock）【保价双11】扫地机器人扫拖一体 P20 Max 自动上下水版自动集尘热水洗拖布擦地拖地 A2950RR</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>3397.23</v>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6">
+        <f>IFERROR(IF(OR(F7="",G7=""),"",(G7-F7)/F7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="5">
+        <f>IF(OR(F7="",K7=""),"",K7*(1-L7)-F7-M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="3">
+        <f>IF(J7="","",IF(J7&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P7" s="3">
+        <f>IF(OR(F7="",G7=""),"",IF(H7&lt;0.15,"放弃",IF(AND(J7&gt;=3,N7&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/4MQRwdxjRz5YjYNYidARYjYNYidARQ_3uiI4idr4VRjmIMQeI.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>jd-2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>裤夹儿童衣帽夹家用无痕多功能收纳神器专用衣架裤架儿童储物收纳 1个装【颜色随机】</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="10">
+        <f>IFERROR(IF(OR(F8="",G8=""),"",(G8-F8)/F8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(OR(F8="",K8=""),"",K8*(1-L8)-F8-M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="7">
+        <f>IF(J8="","",IF(J8&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P8" s="7">
+        <f>IF(OR(F8="",G8=""),"",IF(H8&lt;0.15,"放弃",IF(AND(J8&gt;=3,N8&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>jd-Wl4yE2NZMLRfIB5JUAH6fIB5JUAH64_3QWdDLcL7d2PLwESsR</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>双面胶胶带强力固定双面胶强力固定不留痕手工双面胶学生家用胶带 双面胶带0.5cm*5米（1卷装）</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6">
+        <f>IFERROR(IF(OR(F9="",G9=""),"",(G9-F9)/F9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="5">
+        <f>IF(OR(F9="",K9=""),"",K9*(1-L9)-F9-M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="3">
+        <f>IF(J9="","",IF(J9&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="3">
+        <f>IF(OR(F9="",G9=""),"",IF(H9&lt;0.15,"放弃",IF(AND(J9&gt;=3,N9&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/Wl4yE2NZMLRfIB5JUAH6fIB5JUAH64_3QWdDLcL7d2PLwESsR.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>jd-MOQsWh2qbaweFyODuGJIeFyODuGJIQ_3UIh1p4mYDh9VOtdGU</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>不锈钢汤锅家用特厚蒸锅一体电磁炉煲汤炖锅煮粥锅燃气双耳锅 24CM【带盖】组合加厚底</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="9" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10">
+        <f>IFERROR(IF(OR(F10="",G10=""),"",(G10-F10)/F10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(OR(F10="",K10=""),"",K10*(1-L10)-F10-M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="7">
+        <f>IF(J10="","",IF(J10&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="7">
+        <f>IF(OR(F10="",G10=""),"",IF(H10&lt;0.15,"放弃",IF(AND(J10&gt;=3,N10&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/MOQsWh2qbaweFyODuGJIeFyODuGJIQ_3UIh1p4mYDh9VOtdGU.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>jd-MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6">
+        <f>IFERROR(IF(OR(F11="",G11=""),"",(G11-F11)/F11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" s="5">
+        <f>IF(OR(F11="",K11=""),"",K11*(1-L11)-F11-M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="3">
+        <f>IF(J11="","",IF(J11&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="3">
+        <f>IF(OR(F11="",G11=""),"",IF(H11&lt;0.15,"放弃",IF(AND(J11&gt;=3,N11&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>jd-Zv4tI5eQfUxLXxoPc943LXxoPc9434_3WEwZIiEwNtXjNibpr</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>科沃斯T90 PRO扫地机器人【保价11.11】扫拖一体自动清洗自动集尘热水洗拖布滚筒洗地机器人自动上下水</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="9" t="n">
+        <v>3398.1</v>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10">
+        <f>IFERROR(IF(OR(F12="",G12=""),"",(G12-F12)/F12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(OR(F12="",K12=""),"",K12*(1-L12)-F12-M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="7">
+        <f>IF(J12="","",IF(J12&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="7">
+        <f>IF(OR(F12="",G12=""),"",IF(H12&lt;0.15,"放弃",IF(AND(J12&gt;=3,N12&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="9" t="n"/>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/Zv4tI5eQfUxLXxoPc943LXxoPc9434_3WEwZIiEwNtXjNibpr.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>jd-ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>【3D立体音】汽车蓝牙音箱无线低音炮basix迷你车载户外音响便携 电光绿【颜色随机】</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="5" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="6">
+        <f>IFERROR(IF(OR(F13="",G13=""),"",(G13-F13)/F13),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" s="5">
+        <f>IF(OR(F13="",K13=""),"",K13*(1-L13)-F13-M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="3">
+        <f>IF(J13="","",IF(J13&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="3">
+        <f>IF(OR(F13="",G13=""),"",IF(H13&lt;0.15,"放弃",IF(AND(J13&gt;=3,N13&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>jd-xp4x1bZ260aVz4DRpKfbVz4DRpKfb4_3KLpBNZulGblfhVYxO</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>【特惠限量抢】马卡龙挂钩免打孔轻奢可爱小挂钩 马卡龙挂钩 颜色随机【2个】 默认尺码1</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10">
+        <f>IFERROR(IF(OR(F14="",G14=""),"",(G14-F14)/F14),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="9">
+        <f>IF(OR(F14="",K14=""),"",K14*(1-L14)-F14-M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="7">
+        <f>IF(J14="","",IF(J14&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="7">
+        <f>IF(OR(F14="",G14=""),"",IF(H14&lt;0.15,"放弃",IF(AND(J14&gt;=3,N14&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="9" t="n"/>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/xp4x1bZ260aVz4DRpKfbVz4DRpKfb4_3KLpBNZulGblfhVYxO.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>jd-lfQhPiSzZcdSn23OAcrpSn23OAcrpQ_3ASiIEKC60iVL2Kc9E</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>意大利面方便美食低脂面条番茄黑椒拌面代餐速食非油炸111g/盒 随机口味1盒</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6">
+        <f>IFERROR(IF(OR(F15="",G15=""),"",(G15-F15)/F15),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="5">
+        <f>IF(OR(F15="",K15=""),"",K15*(1-L15)-F15-M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="3">
+        <f>IF(J15="","",IF(J15&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="3">
+        <f>IF(OR(F15="",G15=""),"",IF(H15&lt;0.15,"放弃",IF(AND(J15&gt;=3,N15&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/lfQhPiSzZcdSn23OAcrpSn23OAcrpQ_3ASiIEKC60iVL2Kc9E.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>jd-Wl4yE2NZMLRfIB5JUMOjfIB5JUMOj4_3QWdDLcL7d2cRria1R</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>活力28薰衣草洗衣液 衣物去污渍护色持久留香袋装家庭装实惠装 洗衣液2kg*1袋</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10">
+        <f>IFERROR(IF(OR(F16="",G16=""),"",(G16-F16)/F16),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="9">
+        <f>IF(OR(F16="",K16=""),"",K16*(1-L16)-F16-M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="7">
+        <f>IF(J16="","",IF(J16&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="7">
+        <f>IF(OR(F16="",G16=""),"",IF(H16&lt;0.15,"放弃",IF(AND(J16&gt;=3,N16&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/Wl4yE2NZMLRfIB5JUMOjfIB5JUMOj4_3QWdDLcL7d2cRria1R.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>jd-IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>onneo昂乐软壳桑蚕丝纸尿裤试用装超薄透气婴儿尿不湿 【成长裤旅行装】XL码 4片</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="5" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6">
+        <f>IFERROR(IF(OR(F17="",G17=""),"",(G17-F17)/F17),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="5">
+        <f>IF(OR(F17="",K17=""),"",K17*(1-L17)-F17-M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="3">
+        <f>IF(J17="","",IF(J17&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P17" s="3">
+        <f>IF(OR(F17="",G17=""),"",IF(H17&lt;0.15,"放弃",IF(AND(J17&gt;=3,N17&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>jd-xPQbgrafbUoxvQ0dwkcTxvQ0dwkcTQ_3LZQS3125MrEaBJ0AB</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>拍一发二植物草本配方皮肤舒缓止痒膏外用正品保障 周期装【拍一发二】99%用户好评</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="9" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10">
+        <f>IFERROR(IF(OR(F18="",G18=""),"",(G18-F18)/F18),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="9">
+        <f>IF(OR(F18="",K18=""),"",K18*(1-L18)-F18-M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="7">
+        <f>IF(J18="","",IF(J18&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P18" s="7">
+        <f>IF(OR(F18="",G18=""),"",IF(H18&lt;0.15,"放弃",IF(AND(J18&gt;=3,N18&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/xPQbgrafbUoxvQ0dwkcTxvQ0dwkcTQ_3LZQS3125MrEaBJ0AB.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>jd-wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>理肤泉【孙颖莎推荐】B5面膜PRO+ 10片套装修护补水保湿男士女士护肤品</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="6">
+        <f>IFERROR(IF(OR(F19="",G19=""),"",(G19-F19)/F19),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" s="5">
+        <f>IF(OR(F19="",K19=""),"",K19*(1-L19)-F19-M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="3">
+        <f>IF(J19="","",IF(J19&gt;=3,"是","否"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="3">
+        <f>IF(OR(F19="",G19=""),"",IF(H19&lt;0.15,"放弃",IF(AND(J19&gt;=3,N19&gt;=25),"加仓","观察")))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>待核价</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>用法：①B列ID勿删（核价结果回传就靠它）②得物App核价填G列、购买当天E列记购入日期（月底誊到账单）③卖出后补I/J/K列；「加仓」=价差率≥15%且满3单且单均净利≥25元，公式自动判定。F列券后价来自联盟API，下单前自行复核。核完价把文件交回给助手回传，站点即自动算净利排序。</t>
         </is>
@@ -659,8 +1442,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B21:T21"/>
     <mergeCell ref="B2:T2"/>
-    <mergeCell ref="B7:T7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 16:25 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 16:34 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -611,18 +611,18 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>jd-MHQuhJJgthDWOX9y5MOtWOX9y5MOtQ_3RTWn2HSdluOqXJg5U</t>
+          <t>jd-2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>石头（roborock）【保价双11】扫地机器人扫拖一体 P30 Pro 自动上下水版 滚筒洗地机器人热水洗擦地拖地 A3060RR</t>
+          <t>裤夹儿童衣帽夹家用无痕多功能收纳神器专用衣架裤架儿童储物收纳 1个装【颜色随机】</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="5" t="n">
-        <v>3797.32</v>
+        <v>2.1</v>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="6">
@@ -659,25 +659,25 @@
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MHQuhJJgthDWOX9y5MOtWOX9y5MOtQ_3RTWn2HSdluOqXJg5U.html</t>
+          <t>https://item.jd.com/2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr.html</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>jd-Ee4W5PRJj07hoEn0kh2uhoEn0kh2u4_3tyFw3LoavWozsxaal</t>
+          <t>jd-MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>科沃斯T90S PRO扫地机器人【保价11.11】扫拖一体自动清洗自动集尘热水洗拖布滚筒洗地机器人上下水款</t>
+          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
         </is>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="9" t="n">
-        <v>3698.09</v>
+        <v>12</v>
       </c>
       <c r="G6" s="9" t="n"/>
       <c r="H6" s="10">
@@ -714,25 +714,25 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Ee4W5PRJj07hoEn0kh2uhoEn0kh2u4_3tyFw3LoavWozsxaal.html</t>
+          <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>jd-4MQRwdxjRz5YjYNYidARYjYNYidARQ_3uiI4idr4VRjmIMQeI</t>
+          <t>jd-ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>石头（roborock）【保价双11】扫地机器人扫拖一体 P20 Max 自动上下水版自动集尘热水洗拖布擦地拖地 A2950RR</t>
+          <t>【3D立体音】汽车蓝牙音箱无线低音炮basix迷你车载户外音响便携 电光绿【颜色随机】</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="5" t="n">
-        <v>3397.23</v>
+        <v>9.84</v>
       </c>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="6">
@@ -769,25 +769,25 @@
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/4MQRwdxjRz5YjYNYidARYjYNYidARQ_3uiI4idr4VRjmIMQeI.html</t>
+          <t>https://item.jd.com/ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D.html</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>jd-2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr</t>
+          <t>jd-IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>裤夹儿童衣帽夹家用无痕多功能收纳神器专用衣架裤架儿童储物收纳 1个装【颜色随机】</t>
+          <t>onneo昂乐软壳桑蚕丝纸尿裤试用装超薄透气婴儿尿不湿 【成长裤旅行装】XL码 4片</t>
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="9" t="n">
-        <v>2.1</v>
+        <v>6.98</v>
       </c>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="10">
@@ -824,25 +824,25 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr.html</t>
+          <t>https://item.jd.com/IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ.html</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>jd-Wl4yE2NZMLRfIB5JUAH6fIB5JUAH64_3QWdDLcL7d2PLwESsR</t>
+          <t>jd-wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>双面胶胶带强力固定双面胶强力固定不留痕手工双面胶学生家用胶带 双面胶带0.5cm*5米（1卷装）</t>
+          <t>理肤泉【孙颖莎推荐】B5面膜PRO+ 10片套装修护补水保湿男士女士护肤品</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="5" t="n">
-        <v>2.1</v>
+        <v>238</v>
       </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="6">
@@ -879,25 +879,25 @@
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Wl4yE2NZMLRfIB5JUAH6fIB5JUAH64_3QWdDLcL7d2PLwESsR.html</t>
+          <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>jd-MOQsWh2qbaweFyODuGJIeFyODuGJIQ_3UIh1p4mYDh9VOtdGU</t>
+          <t>jd-2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>不锈钢汤锅家用特厚蒸锅一体电磁炉煲汤炖锅煮粥锅燃气双耳锅 24CM【带盖】组合加厚底</t>
+          <t xml:space="preserve">adidas「小锯齿」D-PAD CLASSIC美高风篮球风板鞋男女阿迪达斯 白色/蓝色/棕色   41  </t>
         </is>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="9" t="n">
-        <v>5.99</v>
+        <v>319</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="10">
@@ -934,25 +934,25 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyODuGJIeFyODuGJIQ_3UIh1p4mYDh9VOtdGU.html</t>
+          <t>https://item.jd.com/2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd.html</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>jd-MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U</t>
+          <t>jd-Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
+          <t>adidas ENTRAP美式校园风运动少年感复古篮球风板鞋男女阿迪达斯</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="5" t="n">
-        <v>12</v>
+        <v>309</v>
       </c>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="6">
@@ -989,25 +989,25 @@
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
+          <t>https://item.jd.com/Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l.html</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>jd-Zv4tI5eQfUxLXxoPc943LXxoPc9434_3WEwZIiEwNtXjNibpr</t>
+          <t>jd-lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>科沃斯T90 PRO扫地机器人【保价11.11】扫拖一体自动清洗自动集尘热水洗拖布滚筒洗地机器人自动上下水</t>
+          <t>adidas「闪回鞋」RESPONSE CL经典贴合老爹鞋男女阿迪达斯三叶草   灰色/深绿色/晶白   42</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="9" t="n">
-        <v>3398.1</v>
+        <v>354</v>
       </c>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="10">
@@ -1044,25 +1044,25 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Zv4tI5eQfUxLXxoPc943LXxoPc9434_3WEwZIiEwNtXjNibpr.html</t>
+          <t>https://item.jd.com/lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB.html</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>jd-ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D</t>
+          <t>jd-ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>【3D立体音】汽车蓝牙音箱无线低音炮basix迷你车载户外音响便携 电光绿【颜色随机】</t>
+          <t xml:space="preserve">adidas 面包鞋 GRAND COURT BASE 00s休闲板鞋平底鞋男女阿迪达斯 黑色/白色/树脂黄(推荐女生选小半码)   42  </t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="5" t="n">
-        <v>9.84</v>
+        <v>219</v>
       </c>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="6">
@@ -1099,25 +1099,25 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D.html</t>
+          <t>https://item.jd.com/ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq.html</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>jd-xp4x1bZ260aVz4DRpKfbVz4DRpKfb4_3KLpBNZulGblfhVYxO</t>
+          <t>jd-rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>【特惠限量抢】马卡龙挂钩免打孔轻奢可爱小挂钩 马卡龙挂钩 颜色随机【2个】 默认尺码1</t>
+          <t>adidas ENTRAP美式校园风运动鞋少年感复古篮球风板鞋阿迪达斯   白色/黑色   42</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="9" t="n">
-        <v>2.1</v>
+        <v>309</v>
       </c>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="10">
@@ -1154,25 +1154,25 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/xp4x1bZ260aVz4DRpKfbVz4DRpKfb4_3KLpBNZulGblfhVYxO.html</t>
+          <t>https://item.jd.com/rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP.html</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>jd-lfQhPiSzZcdSn23OAcrpSn23OAcrpQ_3ASiIEKC60iVL2Kc9E</t>
+          <t>jd-Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>意大利面方便美食低脂面条番茄黑椒拌面代餐速食非油炸111g/盒 随机口味1盒</t>
+          <t>adidas休闲加绒加厚连帽卫衣套头衫单穿上衣男秋冬阿迪达斯轻运动   传奇墨水蓝   XL</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="5" t="n">
-        <v>3.1</v>
+        <v>209</v>
       </c>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="6">
@@ -1209,25 +1209,25 @@
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/lfQhPiSzZcdSn23OAcrpSn23OAcrpQ_3ASiIEKC60iVL2Kc9E.html</t>
+          <t>https://item.jd.com/Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr.html</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>jd-Wl4yE2NZMLRfIB5JUMOjfIB5JUMOj4_3QWdDLcL7d2cRria1R</t>
+          <t>jd-6ZTjQ7b9xSUFdKgYAlF1FdKgYAlF1T_3FGgFy7qtu7rriyvQO</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>活力28薰衣草洗衣液 衣物去污渍护色持久留香袋装家庭装实惠装 洗衣液2kg*1袋</t>
+          <t>钓椅全套全地形多功能折叠钓鱼椅超轻便携筏钓椅钓箱鱼竿渔具盲盒 大盒【钓椅/钓箱/饵料】必得一件</t>
         </is>
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="9" t="n">
-        <v>5.6</v>
+        <v>9.98</v>
       </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="10">
@@ -1264,25 +1264,25 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Wl4yE2NZMLRfIB5JUMOjfIB5JUMOj4_3QWdDLcL7d2cRria1R.html</t>
+          <t>https://item.jd.com/6ZTjQ7b9xSUFdKgYAlF1FdKgYAlF1T_3FGgFy7qtu7rriyvQO.html</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>jd-IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ</t>
+          <t>jd-wAQEbTBH1PTwDjl4bMv6wDjl4bMv6Q_3ioMtB1s3UTLyzrWxX</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>onneo昂乐软壳桑蚕丝纸尿裤试用装超薄透气婴儿尿不湿 【成长裤旅行装】XL码 4片</t>
+          <t>新款电动车摩托车后视镜手机支架户外骑行防震自行车导航支架工厂 车把款+防抖机械卡扣 通用款</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="5" t="n">
-        <v>6.98</v>
+        <v>5.9</v>
       </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="6">
@@ -1319,25 +1319,25 @@
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ.html</t>
+          <t>https://item.jd.com/wAQEbTBH1PTwDjl4bMv6wDjl4bMv6Q_3ioMtB1s3UTLyzrWxX.html</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>jd-xPQbgrafbUoxvQ0dwkcTxvQ0dwkcTQ_3LZQS3125MrEaBJ0AB</t>
+          <t>jd-MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>拍一发二植物草本配方皮肤舒缓止痒膏外用正品保障 周期装【拍一发二】99%用户好评</t>
+          <t xml:space="preserve">adidas 600蓬保暖连帽鸭绒羽绒服夹克外套男女秋冬阿迪达斯轻运动 黑色(推荐选大一码)   M  </t>
         </is>
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="9" t="n">
-        <v>39.9</v>
+        <v>519</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="10">
@@ -1374,25 +1374,25 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/xPQbgrafbUoxvQ0dwkcTxvQ0dwkcTQ_3LZQS3125MrEaBJ0AB.html</t>
+          <t>https://item.jd.com/MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU.html</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>jd-wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX</t>
+          <t>jd-6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>理肤泉【孙颖莎推荐】B5面膜PRO+ 10片套装修护补水保湿男士女士护肤品</t>
+          <t>adidas ENTRAP少年感复古篮球风板鞋平底鞋男女阿迪达斯轻运动   亮白/浅灰/黑色/浅蓝   37</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="5" t="n">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="6">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
+          <t>https://item.jd.com/6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T.html</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 16:34 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 16:44 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -611,18 +611,18 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>jd-2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr</t>
+          <t>jd-MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>裤夹儿童衣帽夹家用无痕多功能收纳神器专用衣架裤架儿童储物收纳 1个装【颜色随机】</t>
+          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="5" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="6">
@@ -659,25 +659,25 @@
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/2OQl0HpY85vWfgyFzBX5WfgyFzBX5Q_3HJs6XxZN4H5YWIspr.html</t>
+          <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>jd-MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U</t>
+          <t>jd-wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
+          <t>理肤泉【孙颖莎推荐】B5面膜PRO+ 10片套装修护补水保湿男士女士护肤品</t>
         </is>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="9" t="n">
-        <v>12</v>
+        <v>238</v>
       </c>
       <c r="G6" s="9" t="n"/>
       <c r="H6" s="10">
@@ -714,25 +714,25 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
+          <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>jd-ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D</t>
+          <t>jd-2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>【3D立体音】汽车蓝牙音箱无线低音炮basix迷你车载户外音响便携 电光绿【颜色随机】</t>
+          <t xml:space="preserve">adidas「小锯齿」D-PAD CLASSIC美高风篮球风板鞋男女阿迪达斯 白色/蓝色/棕色   41  </t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="5" t="n">
-        <v>9.84</v>
+        <v>319</v>
       </c>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="6">
@@ -769,25 +769,25 @@
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/ejQZewyNLyU04AjQ6Rwv04AjQ6RwvQ_3vbTPlG3J3w1IE6b2D.html</t>
+          <t>https://item.jd.com/2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd.html</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>jd-IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ</t>
+          <t>jd-Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>onneo昂乐软壳桑蚕丝纸尿裤试用装超薄透气婴儿尿不湿 【成长裤旅行装】XL码 4片</t>
+          <t>adidas ENTRAP美式校园风运动少年感复古篮球风板鞋男女阿迪达斯</t>
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="9" t="n">
-        <v>6.98</v>
+        <v>309</v>
       </c>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="10">
@@ -824,25 +824,25 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/IpQGCM3WUs3J6spIV7NVJ6spIV7NVQ_3zxzkH2BNoM4fX9cpQ.html</t>
+          <t>https://item.jd.com/Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l.html</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>jd-wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX</t>
+          <t>jd-lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>理肤泉【孙颖莎推荐】B5面膜PRO+ 10片套装修护补水保湿男士女士护肤品</t>
+          <t>adidas「闪回鞋」RESPONSE CL经典贴合老爹鞋男女阿迪达斯三叶草   灰色/深绿色/晶白   42</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="5" t="n">
-        <v>238</v>
+        <v>354</v>
       </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="6">
@@ -879,25 +879,25 @@
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
+          <t>https://item.jd.com/lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB.html</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>jd-2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd</t>
+          <t>jd-ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">adidas「小锯齿」D-PAD CLASSIC美高风篮球风板鞋男女阿迪达斯 白色/蓝色/棕色   41  </t>
+          <t xml:space="preserve">adidas 面包鞋 GRAND COURT BASE 00s休闲板鞋平底鞋男女阿迪达斯 黑色/白色/树脂黄(推荐女生选小半码)   42  </t>
         </is>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="9" t="n">
-        <v>319</v>
+        <v>219</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="10">
@@ -934,19 +934,19 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd.html</t>
+          <t>https://item.jd.com/ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq.html</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>jd-Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l</t>
+          <t>jd-rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>adidas ENTRAP美式校园风运动少年感复古篮球风板鞋男女阿迪达斯</t>
+          <t>adidas ENTRAP美式校园风运动鞋少年感复古篮球风板鞋阿迪达斯   白色/黑色   42</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -989,25 +989,25 @@
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l.html</t>
+          <t>https://item.jd.com/rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP.html</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>jd-lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB</t>
+          <t>jd-Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>adidas「闪回鞋」RESPONSE CL经典贴合老爹鞋男女阿迪达斯三叶草   灰色/深绿色/晶白   42</t>
+          <t>adidas休闲加绒加厚连帽卫衣套头衫单穿上衣男秋冬阿迪达斯轻运动   传奇墨水蓝   XL</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="9" t="n">
-        <v>354</v>
+        <v>209</v>
       </c>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="10">
@@ -1044,25 +1044,25 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB.html</t>
+          <t>https://item.jd.com/Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr.html</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>jd-ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq</t>
+          <t>jd-MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">adidas 面包鞋 GRAND COURT BASE 00s休闲板鞋平底鞋男女阿迪达斯 黑色/白色/树脂黄(推荐女生选小半码)   42  </t>
+          <t xml:space="preserve">adidas 600蓬保暖连帽鸭绒羽绒服夹克外套男女秋冬阿迪达斯轻运动 黑色(推荐选大一码)   M  </t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="5" t="n">
-        <v>219</v>
+        <v>519</v>
       </c>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="6">
@@ -1099,25 +1099,25 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq.html</t>
+          <t>https://item.jd.com/MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU.html</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>jd-rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP</t>
+          <t>jd-6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>adidas ENTRAP美式校园风运动鞋少年感复古篮球风板鞋阿迪达斯   白色/黑色   42</t>
+          <t>adidas ENTRAP少年感复古篮球风板鞋平底鞋男女阿迪达斯轻运动   亮白/浅灰/黑色/浅蓝   37</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="9" t="n">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="10">
@@ -1154,25 +1154,25 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP.html</t>
+          <t>https://item.jd.com/6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T.html</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>jd-Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr</t>
+          <t>jd-MOQsWh2qbaweFyOoCB9oeFyOoCB9oQ_3UIh1p4mYDh82NLJwU</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>adidas休闲加绒加厚连帽卫衣套头衫单穿上衣男秋冬阿迪达斯轻运动   传奇墨水蓝   XL</t>
+          <t xml:space="preserve">adidas「小锯齿」D-PAD CLASSIC美高风篮球风板鞋男女阿迪达斯 浅灰/黑色/浅猩红   39  </t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="5" t="n">
-        <v>209</v>
+        <v>319</v>
       </c>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="6">
@@ -1209,25 +1209,25 @@
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr.html</t>
+          <t>https://item.jd.com/MOQsWh2qbaweFyOoCB9oeFyOoCB9oQ_3UIh1p4mYDh82NLJwU.html</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>jd-6ZTjQ7b9xSUFdKgYAlF1FdKgYAlF1T_3FGgFy7qtu7rriyvQO</t>
+          <t>jd-BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>钓椅全套全地形多功能折叠钓鱼椅超轻便携筏钓椅钓箱鱼竿渔具盲盒 大盒【钓椅/钓箱/饵料】必得一件</t>
+          <t>匡威（Converse）莫尔登All Star夏季男女板鞋中帮帆布小白鞋A00812C A00812C 42.5</t>
         </is>
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="9" t="n">
-        <v>9.98</v>
+        <v>249</v>
       </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="10">
@@ -1264,25 +1264,25 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/6ZTjQ7b9xSUFdKgYAlF1FdKgYAlF1T_3FGgFy7qtu7rriyvQO.html</t>
+          <t>https://item.jd.com/BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK.html</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>jd-wAQEbTBH1PTwDjl4bMv6wDjl4bMv6Q_3ioMtB1s3UTLyzrWxX</t>
+          <t>jd-WaTNAjuVlJUL7cXFsU8LL7cXFsU8LT_sweEl8TjnbzVqQVhiu</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>新款电动车摩托车后视镜手机支架户外骑行防震自行车导航支架工厂 车把款+防抖机械卡扣 通用款</t>
+          <t>adidas ENTRAP美式校园风运动鞋少年感复古篮球风板鞋阿迪达斯   白色/金属暗银   37</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="5" t="n">
-        <v>5.9</v>
+        <v>309</v>
       </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="6">
@@ -1319,25 +1319,25 @@
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/wAQEbTBH1PTwDjl4bMv6wDjl4bMv6Q_3ioMtB1s3UTLyzrWxX.html</t>
+          <t>https://item.jd.com/WaTNAjuVlJUL7cXFsU8LL7cXFsU8LT_sweEl8TjnbzVqQVhiu.html</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>jd-MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU</t>
+          <t>jd-Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">adidas 600蓬保暖连帽鸭绒羽绒服夹克外套男女秋冬阿迪达斯轻运动 黑色(推荐选大一码)   M  </t>
+          <t>雪中飞秋冬新款男式轻薄羽绒服马甲基础男士短款羽绒秋马甲质感 宝石黑|8086 XL 180/100A</t>
         </is>
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="9" t="n">
-        <v>519</v>
+        <v>79</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="10">
@@ -1374,25 +1374,25 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU.html</t>
+          <t>https://item.jd.com/Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379.html</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>jd-6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T</t>
+          <t>jd-MOQsWh2qbaweFyO30JdkeFyO30JdkQ_3UIh1p4mYDh91P3O0U</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>adidas ENTRAP少年感复古篮球风板鞋平底鞋男女阿迪达斯轻运动   亮白/浅灰/黑色/浅蓝   37</t>
+          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="5" t="n">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="6">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T.html</t>
+          <t>https://item.jd.com/MOQsWh2qbaweFyO30JdkeFyO30JdkQ_3UIh1p4mYDh91P3O0U.html</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 16:44 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 18:09 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 18:09 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-10 22:21 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-10 22:21 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-11 03:53 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-11 03:53 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-11 07:20 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-11 07:20 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-11 11:53 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-11 11:53 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-11 18:42 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T21"/>
+  <dimension ref="B2:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -502,12 +502,13 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-11 18:42 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-12 01:27 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -605,6 +606,11 @@
       <c r="T4" s="2" t="inlineStr">
         <is>
           <t>门道链接</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>得物分享链接</t>
         </is>
       </c>
     </row>
@@ -662,6 +668,11 @@
           <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
         </is>
       </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="7" t="inlineStr">
@@ -717,6 +728,11 @@
           <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
         </is>
       </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
@@ -772,6 +788,11 @@
           <t>https://item.jd.com/2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd.html</t>
         </is>
       </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="7" t="inlineStr">
@@ -827,6 +848,11 @@
           <t>https://item.jd.com/Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l.html</t>
         </is>
       </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
@@ -882,6 +908,11 @@
           <t>https://item.jd.com/lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB.html</t>
         </is>
       </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
@@ -937,6 +968,11 @@
           <t>https://item.jd.com/ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq.html</t>
         </is>
       </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
@@ -992,6 +1028,11 @@
           <t>https://item.jd.com/rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP.html</t>
         </is>
       </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="7" t="inlineStr">
@@ -1047,6 +1088,11 @@
           <t>https://item.jd.com/Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr.html</t>
         </is>
       </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
@@ -1102,6 +1148,11 @@
           <t>https://item.jd.com/MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU.html</t>
         </is>
       </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="7" t="inlineStr">
@@ -1157,22 +1208,27 @@
           <t>https://item.jd.com/6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T.html</t>
         </is>
       </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>jd-MOQsWh2qbaweFyOoCB9oeFyOoCB9oQ_3UIh1p4mYDh82NLJwU</t>
+          <t>jd-BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">adidas「小锯齿」D-PAD CLASSIC美高风篮球风板鞋男女阿迪达斯 浅灰/黑色/浅猩红   39  </t>
+          <t>匡威（Converse）莫尔登All Star夏季男女板鞋中帮帆布小白鞋A00812C A00812C 42.5</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="5" t="n">
-        <v>319</v>
+        <v>249</v>
       </c>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="6">
@@ -1209,25 +1265,30 @@
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyOoCB9oeFyOoCB9oQ_3UIh1p4mYDh82NLJwU.html</t>
+          <t>https://item.jd.com/BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK.html</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>jd-BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK</t>
+          <t>jd-Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>匡威（Converse）莫尔登All Star夏季男女板鞋中帮帆布小白鞋A00812C A00812C 42.5</t>
+          <t>雪中飞秋冬新款男式轻薄羽绒服马甲基础男士短款羽绒秋马甲质感 宝石黑|8086 XL 180/100A</t>
         </is>
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="9" t="n">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="10">
@@ -1264,25 +1325,30 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK.html</t>
+          <t>https://item.jd.com/Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379.html</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>jd-WaTNAjuVlJUL7cXFsU8LL7cXFsU8LT_sweEl8TjnbzVqQVhiu</t>
+          <t>jd-05QSuAGkxEvcCqMrws50cCqMrws50Q_3ghOeVWBK5SCER5KYF</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>adidas ENTRAP美式校园风运动鞋少年感复古篮球风板鞋阿迪达斯   白色/金属暗银   37</t>
+          <t>理肤泉【黄子弘凡同款】B5霜40ml+B5水50ml套装修护保湿面霜护肤品</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="5" t="n">
-        <v>309</v>
+        <v>90</v>
       </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="6">
@@ -1319,25 +1385,30 @@
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/WaTNAjuVlJUL7cXFsU8LL7cXFsU8LT_sweEl8TjnbzVqQVhiu.html</t>
+          <t>https://item.jd.com/05QSuAGkxEvcCqMrws50cCqMrws50Q_3ghOeVWBK5SCER5KYF.html</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>jd-Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379</t>
+          <t>jd-wAQEbTBH1PTwDjlR5U9hwDjlR5U9hQ_3ioMtB1s3UTa9rGCVX</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>雪中飞秋冬新款男式轻薄羽绒服马甲基础男士短款羽绒秋马甲质感 宝石黑|8086 XL 180/100A</t>
+          <t>林清轩精华油4.0山茶花面部精华油以油养肤修护屏障淡纹节日礼物送女友 50ml精华油</t>
         </is>
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="9" t="n">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="10">
@@ -1374,25 +1445,30 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>https://item.jd.com/Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379.html</t>
+          <t>https://item.jd.com/wAQEbTBH1PTwDjlR5U9hwDjlR5U9hQ_3ioMtB1s3UTa9rGCVX.html</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>jd-MOQsWh2qbaweFyO30JdkeFyO30JdkQ_3UIh1p4mYDh91P3O0U</t>
+          <t>jd-qp4cyX8p7tnYt0oi4bONYt0oi4bON4_3JKSxG0iK1ccJCJx3B</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>林清轩面霜山茶花50ml清爽保湿干皮好吸收锁水送女友节日礼物 滋养面霜50g</t>
+          <t>薇诺娜【全红婵同款】薇诺娜舒敏保湿特护精萃水120ml爽肤水修护礼物</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="5" t="n">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="6">
@@ -1429,21 +1505,26 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyO30JdkeFyO30JdkQ_3UIh1p4mYDh91P3O0U.html</t>
+          <t>https://item.jd.com/qp4cyX8p7tnYt0oi4bONYt0oi4bON4_3JKSxG0iK1ccJCJx3B.html</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>← App搜同款·分享·复制链接粘这里</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>用法：①B列ID勿删（核价结果回传就靠它）②得物App核价填G列、购买当天E列记购入日期（月底誊到账单）③卖出后补I/J/K列；「加仓」=价差率≥15%且满3单且单均净利≥25元，公式自动判定。F列券后价来自联盟API，下单前自行复核。核完价把文件交回给助手回传，站点即自动算净利排序。</t>
+          <t>用法：①B列ID勿删②得物App搜同款→点分享→复制链接→粘到U列，回传后自动核价并每天跟踪价格（比手填G列省事，G列手填也仍然有效）；E列记购入日期，卖出后补I/J/K列；「加仓」=价差率≥15%且满3单且单均净利≥25元，公式自动判定。F列券后价来自联盟API，下单前自行复核。核完价把文件交回给助手回传，站点即自动算净利排序。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B21:T21"/>
-    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="B21:U21"/>
+    <mergeCell ref="B2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-12 01:27 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-12 07:36 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-12 07:36 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-12 12:17 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-12 12:17 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-13 01:35 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-13 01:35 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-13 10:04 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-13 10:04 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-13 19:41 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-13 19:41 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-14 03:06 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-14 03:06 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-14 07:51 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-14 07:51 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-14 11:39 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-14 11:39 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-14 17:30 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-14 17:30 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-15 00:32 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>参考净利(元)</t>
+          <t>预估净利(元)</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>门道链接</t>
+          <t>货源链接</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -663,11 +663,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyODu3mAeFyODu3mAQ_3UIh1p4mYDh91P3O0U.html</t>
-        </is>
-      </c>
+      <c r="T5" s="4" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -723,11 +719,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/wAQEbTBH1PTwDjlS1ZkowDjlS1ZkoQ_3ioMtB1s3UEDhvicGX.html</t>
-        </is>
-      </c>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -783,11 +775,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/2qQeKGOo8tE6mJQZev8r6mJQZev8rQ_31Q63C0rRqG7aq0ixd.html</t>
-        </is>
-      </c>
+      <c r="T7" s="4" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -843,11 +831,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/Ee4W5PRJj07hoEncY1UKhoEncY1UK4_3tyFw3LoavWozhLM1l.html</t>
-        </is>
-      </c>
+      <c r="T8" s="8" t="inlineStr"/>
       <c r="U8" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -903,11 +887,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/lu4dUZrMDw2A7SkkK4bEA7SkkK4bE4_3PAq5P3t9OZB81P8CB.html</t>
-        </is>
-      </c>
+      <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -963,11 +943,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/ph4N7kTSnkdNgGrKPjB3NgGrKPjB34_373ZMXtqaAk0KmXDWq.html</t>
-        </is>
-      </c>
+      <c r="T10" s="8" t="inlineStr"/>
       <c r="U10" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1023,11 +999,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/rkQ3qFFUDGBzsautQu9azsautQu9aQ_336U75gP0EF9FWl4dP.html</t>
-        </is>
-      </c>
+      <c r="T11" s="4" t="inlineStr"/>
       <c r="U11" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1083,11 +1055,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/Zv4tI5eQfUxLXxoG0Du1LXxoG0Du14_3WEwZIiEwN5h2FcPsr.html</t>
-        </is>
-      </c>
+      <c r="T12" s="8" t="inlineStr"/>
       <c r="U12" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1143,11 +1111,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/MOQsWh2qbaweFyOoCBqWeFyOoCBqWQ_3UIh1p4mYDhAJ7V5KU.html</t>
-        </is>
-      </c>
+      <c r="T13" s="4" t="inlineStr"/>
       <c r="U13" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1203,11 +1167,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/6xXY8S53fHrbKnGqqmr0bKnGqqmr0X_3opDrtnmotSpoCTT1T.html</t>
-        </is>
-      </c>
+      <c r="T14" s="8" t="inlineStr"/>
       <c r="U14" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1263,11 +1223,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/BFQAJ8UmtDqw9oKn7aP7w9oKn7aP7Q_3hj3LwOh1a8eoG8JoK.html</t>
-        </is>
-      </c>
+      <c r="T15" s="4" t="inlineStr"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1323,11 +1279,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/Ip47p46sefZQZCRp3iWYQZCRp3iWY4_3NM1doBNOJ4NbKm379.html</t>
-        </is>
-      </c>
+      <c r="T16" s="8" t="inlineStr"/>
       <c r="U16" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1383,11 +1335,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/05QSuAGkxEvcCqMrws50cCqMrws50Q_3ghOeVWBK5SCER5KYF.html</t>
-        </is>
-      </c>
+      <c r="T17" s="4" t="inlineStr"/>
       <c r="U17" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1443,11 +1391,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/wAQEbTBH1PTwDjlR5U9hwDjlR5U9hQ_3ioMtB1s3UTa9rGCVX.html</t>
-        </is>
-      </c>
+      <c r="T18" s="8" t="inlineStr"/>
       <c r="U18" s="7" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1503,11 +1447,7 @@
           <t>待核价</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>https://item.jd.com/qp4cyX8p7tnYt0oi4bONYt0oi4bON4_3JKSxG0iK1ccJCJx3B.html</t>
-        </is>
-      </c>
+      <c r="T19" s="4" t="inlineStr"/>
       <c r="U19" s="3" t="inlineStr">
         <is>
           <t>← App搜同款·分享·复制链接粘这里</t>
@@ -1517,7 +1457,7 @@
     <row r="21" ht="42" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>用法：①B列ID勿删②得物App搜同款→点分享→复制链接→粘到U列，回传后自动核价并每天跟踪价格（比手填G列省事，G列手填也仍然有效）；E列记购入日期，卖出后补I/J/K列；「加仓」=价差率≥15%且满3单且单均净利≥25元，公式自动判定。F列券后价来自联盟API，下单前自行复核。核完价把文件交回给助手回传，站点即自动算净利排序。</t>
+          <t>B列ID勿删。F列为联盟参考价，指定规格和券条件需复核；G列可记当前得物报价。分享链接只能补充款式信息，不能自动获取实时卖价。正式核价需记录双方货号、颜色、尺码、时间及截图依据，按INDEPENDENT.md写入verified_quotes.json；超过24小时重新核价。默认费率仅作估算，实际费用需核实。</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-15 00:32 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-15 07:03 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-15 07:03 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-15 11:05 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-15 11:05 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-15 16:54 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-15 16:54 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-16 00:19 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-16 00:19 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-16 06:58 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-16 06:58 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-16 11:03 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-16 11:03 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-16 16:49 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-16 16:49 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-17 00:06 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-17 00:06 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-17 03:36 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-17 03:36 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-17 06:34 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-17 06:34 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-17 10:55 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-17 10:55 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-17 16:20 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-17 16:20 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-17 22:59 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-17 22:59 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-18 02:13 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-18 02:13 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-18 06:03 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-18 06:03 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-18 10:57 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-18 10:57 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-18 16:37 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-18 16:37 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-18 23:25 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-18 23:25 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-19 02:32 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-19 02:32 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-19 06:18 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-19 06:18 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-19 11:09 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-19 11:09 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-19 17:39 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-19 17:39 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-20 02:22 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-20 02:22 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-20 07:23 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-20 07:23 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-20 11:19 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-20 11:19 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-20 17:11 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-20 17:11 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-21 00:23 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-21 00:23 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-21 07:00 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-21 07:00 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-21 11:14 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-21 11:14 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-21 17:11 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-21 17:11 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-22 00:38 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-22 00:38 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-22 07:06 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-22 07:06 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-22 11:12 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-22 11:12 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-22 17:14 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-22 17:14 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-23 00:39 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-23 00:39 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-23 07:03 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-23 07:03 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-23 11:17 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-23 11:17 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-23 17:09 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-23 17:09 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-24 00:29 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-24 00:29 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-24 06:58 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-24 06:58 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-24 11:12 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-24 11:12 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-24 16:42 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-24 16:42 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-24 23:25 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-24 23:25 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-25 02:39 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-25 02:39 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-25 06:19 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-25 06:19 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-25 11:06 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-25 11:06 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-25 17:01 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-25 17:01 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-25 23:35 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-25 23:35 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-26 02:48 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-26 02:48 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-26 06:22 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-26 06:22 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-26 11:06 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-26 11:06 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-26 17:44 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-26 17:44 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-27 02:17 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-27 02:17 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-27 07:38 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-27 07:38 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-27 11:38 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-27 11:38 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-27 17:39 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-27 17:39 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-28 01:29 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-28 01:29 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-28 07:32 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-28 07:32 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-28 11:53 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-28 11:53 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-28 18:24 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-28 18:24 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-29 01:56 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-29 01:56 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-29 07:57 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-29 07:57 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-29 12:16 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-29 12:16 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-29 23:01 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-29 23:01 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-30 04:55 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-30 04:55 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-30 12:17 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-30 12:17 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-30 22:53 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-30 22:53 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-31 04:27 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-31 04:27 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-31 11:59 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-31 11:59 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-10-31 18:16 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>

--- a/site/checklist.xlsx
+++ b/site/checklist.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>待核价清单（2026-10-31 18:16 生成 · 线报站自动导出）</t>
+          <t>待核价清单（2026-11-01 00:51 生成 · 线报站自动导出）</t>
         </is>
       </c>
     </row>
